--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.61821363743218</v>
+        <v>10.17545971608273</v>
       </c>
       <c r="D2" t="n">
-        <v>62.55347670929679</v>
+        <v>10.16493996526073</v>
       </c>
       <c r="E2" t="n">
-        <v>4.491718608356543</v>
+        <v>0.7299042738579384</v>
       </c>
       <c r="F2" t="n">
-        <v>4.568569213970704</v>
+        <v>0.7423924972702398</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.60165085414526</v>
+        <v>11.63526826379861</v>
       </c>
       <c r="D3" t="n">
-        <v>71.6906151372382</v>
+        <v>11.64972495980121</v>
       </c>
       <c r="E3" t="n">
-        <v>4.491718608356543</v>
+        <v>0.7299042738579384</v>
       </c>
       <c r="F3" t="n">
-        <v>4.568569213970704</v>
+        <v>0.7423924972702398</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
